--- a/out_FPT/compare_sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26.xlsx
+++ b/out_FPT/compare_sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,60 +464,80 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>Diesel_Air_kg_h</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Diesel_Air_kg_h_kW</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>Diesel_n_th_pct</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>E94H6_Speed_RPM</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>E94H6_Power_kW</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>E94H6_Consumo_kg_h</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>E94H6_Consumo_L_h</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>E94H6_Custo_R_h</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>E94H6_Custo_R_kWh</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>E94H6_Air_kg_h</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>E94H6_Air_kg_h_kW</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>E94H6_n_th_pct</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_R_h</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_pct</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_R_kWh</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_R_kWh_pct</t>
         </is>
@@ -556,39 +576,51 @@
         <v>1.267684274555436</v>
       </c>
       <c r="J2" t="n">
+        <v>818.1010032</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.862228663873061</v>
+      </c>
+      <c r="L2" t="n">
         <v>43.21582376606398</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>899.965</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>153.0359</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>59.591</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>73.66007416563659</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>154.6861557478368</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>1.010783455044449</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
+        <v>493.8484</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.227010132916525</v>
+      </c>
+      <c r="U2" t="n">
         <v>37.58201332579686</v>
       </c>
-      <c r="R2" t="n">
+      <c r="V2" t="n">
         <v>-113.8359507901702</v>
       </c>
-      <c r="S2" t="n">
+      <c r="W2" t="n">
         <v>-42.39351175135284</v>
       </c>
-      <c r="T2" t="n">
+      <c r="X2" t="n">
         <v>-0.256900819510987</v>
       </c>
-      <c r="U2" t="n">
+      <c r="Y2" t="n">
         <v>-20.2653629667434</v>
       </c>
     </row>
@@ -625,39 +657,51 @@
         <v>1.231474195136687</v>
       </c>
       <c r="J3" t="n">
+        <v>1066.51589024</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.136611124591413</v>
+      </c>
+      <c r="L3" t="n">
         <v>44.48653525713356</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>999.899</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>182.1889</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>70.161</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>86.72558714462299</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>182.1237330037083</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>0.9996423108307273</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
+        <v>577.2861</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.168612906713856</v>
+      </c>
+      <c r="U3" t="n">
         <v>38.00086977651749</v>
       </c>
-      <c r="R3" t="n">
+      <c r="V3" t="n">
         <v>-135.379352970688</v>
       </c>
-      <c r="S3" t="n">
+      <c r="W3" t="n">
         <v>-42.63875185818039</v>
       </c>
-      <c r="T3" t="n">
+      <c r="X3" t="n">
         <v>-0.2318318843059595</v>
       </c>
-      <c r="U3" t="n">
+      <c r="Y3" t="n">
         <v>-18.82555763015622</v>
       </c>
     </row>
@@ -694,39 +738,51 @@
         <v>1.222679603673823</v>
       </c>
       <c r="J4" t="n">
+        <v>1268.3126194</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.439412673420192</v>
+      </c>
+      <c r="L4" t="n">
         <v>44.80652170493985</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>1100.059</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>236.6207</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>90.709</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>112.1248454882571</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>235.4621755253399</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>0.9951038752118473</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
+        <v>732.7568</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.096756961669034</v>
+      </c>
+      <c r="U4" t="n">
         <v>38.17418283984513</v>
       </c>
-      <c r="R4" t="n">
+      <c r="V4" t="n">
         <v>-113.849790921741</v>
       </c>
-      <c r="S4" t="n">
+      <c r="W4" t="n">
         <v>-32.5925825215005</v>
       </c>
-      <c r="T4" t="n">
+      <c r="X4" t="n">
         <v>-0.2275757284619757</v>
       </c>
-      <c r="U4" t="n">
+      <c r="Y4" t="n">
         <v>-18.61286699951254</v>
       </c>
     </row>
@@ -763,39 +819,51 @@
         <v>1.229983848493006</v>
       </c>
       <c r="J5" t="n">
+        <v>1394.40211569</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.351854783728491</v>
+      </c>
+      <c r="L5" t="n">
         <v>44.54043869545165</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>1199.668</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>261.7221</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>99.86499999999999</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>123.442521631644</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>259.2292954264524</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>0.9904753760819295</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
+        <v>802.8339999999999</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.067505571749577</v>
+      </c>
+      <c r="U5" t="n">
         <v>38.35257109292667</v>
       </c>
-      <c r="R5" t="n">
+      <c r="V5" t="n">
         <v>-134.8767043913437</v>
       </c>
-      <c r="S5" t="n">
+      <c r="W5" t="n">
         <v>-34.22345877852664</v>
       </c>
-      <c r="T5" t="n">
+      <c r="X5" t="n">
         <v>-0.2395084724110762</v>
       </c>
-      <c r="U5" t="n">
+      <c r="Y5" t="n">
         <v>-19.47248922858016</v>
       </c>
     </row>
@@ -832,39 +900,51 @@
         <v>1.236787667079175</v>
       </c>
       <c r="J6" t="n">
+        <v>1501.12002116</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.337543110523877</v>
+      </c>
+      <c r="L6" t="n">
         <v>44.29541275227747</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>1300.024</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>280.1731</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>107.281</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>132.6093943139679</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>278.4797280593326</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>0.9939559795688186</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
+        <v>859.04</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.066104490402541</v>
+      </c>
+      <c r="U6" t="n">
         <v>38.21826927733208</v>
       </c>
-      <c r="R6" t="n">
+      <c r="V6" t="n">
         <v>-149.5429293920391</v>
       </c>
-      <c r="S6" t="n">
+      <c r="W6" t="n">
         <v>-34.9380872224104</v>
       </c>
-      <c r="T6" t="n">
+      <c r="X6" t="n">
         <v>-0.2428316875103567</v>
       </c>
-      <c r="U6" t="n">
+      <c r="Y6" t="n">
         <v>-19.63406443757911</v>
       </c>
     </row>
@@ -901,39 +981,51 @@
         <v>1.247317208041472</v>
       </c>
       <c r="J7" t="n">
+        <v>1591.65581007</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.332122930443129</v>
+      </c>
+      <c r="L7" t="n">
         <v>43.92148191895775</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>1400.075</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>300.4143</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>115.281</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>142.4981458590853</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>299.2461063040791</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>0.9961113911823742</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
+        <v>924.624</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.07782951743642</v>
+      </c>
+      <c r="U7" t="n">
         <v>38.1355715969526</v>
       </c>
-      <c r="R7" t="n">
+      <c r="V7" t="n">
         <v>-159.0279808018529</v>
       </c>
-      <c r="S7" t="n">
+      <c r="W7" t="n">
         <v>-34.70149966500132</v>
       </c>
-      <c r="T7" t="n">
+      <c r="X7" t="n">
         <v>-0.251205816859098</v>
       </c>
-      <c r="U7" t="n">
+      <c r="Y7" t="n">
         <v>-20.13968982706007</v>
       </c>
     </row>
@@ -970,39 +1062,51 @@
         <v>1.264441188607331</v>
       </c>
       <c r="J8" t="n">
+        <v>1689.92398591</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.347692441495634</v>
+      </c>
+      <c r="L8" t="n">
         <v>43.32666532362657</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>1500.016</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>301.1655</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>116.68</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>144.2274412855377</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>302.8776266996292</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>1.00568500276303</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
+        <v>933.568</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.099850414473105</v>
+      </c>
+      <c r="U8" t="n">
         <v>37.77254028111073</v>
       </c>
-      <c r="R8" t="n">
+      <c r="V8" t="n">
         <v>-188.6036641584247</v>
       </c>
-      <c r="S8" t="n">
+      <c r="W8" t="n">
         <v>-38.37453585041873</v>
       </c>
-      <c r="T8" t="n">
+      <c r="X8" t="n">
         <v>-0.2587561858443008</v>
       </c>
-      <c r="U8" t="n">
+      <c r="Y8" t="n">
         <v>-20.46407442083548</v>
       </c>
     </row>
@@ -1039,39 +1143,51 @@
         <v>1.280515994961004</v>
       </c>
       <c r="J9" t="n">
+        <v>1757.33848801</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.456480230588814</v>
+      </c>
+      <c r="L9" t="n">
         <v>42.7827691460166</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>1600.038</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>300.3554</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>117.308</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>145.0037082818294</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>304.5077873918418</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>1.013824913392074</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
+        <v>939.66</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.12849377770468</v>
+      </c>
+      <c r="U9" t="n">
         <v>37.46926789348365</v>
       </c>
-      <c r="R9" t="n">
+      <c r="V9" t="n">
         <v>-200.4422911503153</v>
       </c>
-      <c r="S9" t="n">
+      <c r="W9" t="n">
         <v>-39.69546687249021</v>
       </c>
-      <c r="T9" t="n">
+      <c r="X9" t="n">
         <v>-0.2666910815689301</v>
       </c>
-      <c r="U9" t="n">
+      <c r="Y9" t="n">
         <v>-20.8268450076683</v>
       </c>
     </row>
@@ -1108,39 +1224,51 @@
         <v>1.288301253393223</v>
       </c>
       <c r="J10" t="n">
+        <v>1781.48985339</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.53941845037895</v>
+      </c>
+      <c r="L10" t="n">
         <v>42.52423108019509</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>1699.999</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>296.0968</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>117.119</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>144.770086526576</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>304.0171817058097</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>1.026749298559828</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
+        <v>935.774</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.16036512383788</v>
+      </c>
+      <c r="U10" t="n">
         <v>36.99761697452185</v>
       </c>
-      <c r="R10" t="n">
+      <c r="V10" t="n">
         <v>-201.5752495973791</v>
       </c>
-      <c r="S10" t="n">
+      <c r="W10" t="n">
         <v>-39.86911929789162</v>
       </c>
-      <c r="T10" t="n">
+      <c r="X10" t="n">
         <v>-0.2615519548333953</v>
       </c>
-      <c r="U10" t="n">
+      <c r="Y10" t="n">
         <v>-20.30208028941215</v>
       </c>
     </row>
@@ -1177,39 +1305,51 @@
         <v>1.305177527482162</v>
       </c>
       <c r="J11" t="n">
+        <v>1839.49337931</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.661451409354044</v>
+      </c>
+      <c r="L11" t="n">
         <v>41.97438206424157</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>1799.979</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>291.8231</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>116.542</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>144.0568603213844</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>302.5194066749073</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>1.036653392671476</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
+        <v>931.751</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.192862388207102</v>
+      </c>
+      <c r="U11" t="n">
         <v>36.64414503972399</v>
       </c>
-      <c r="R11" t="n">
+      <c r="V11" t="n">
         <v>-212.5273480354093</v>
       </c>
-      <c r="S11" t="n">
+      <c r="W11" t="n">
         <v>-41.26370006057864</v>
       </c>
-      <c r="T11" t="n">
+      <c r="X11" t="n">
         <v>-0.2685241348106859</v>
       </c>
-      <c r="U11" t="n">
+      <c r="Y11" t="n">
         <v>-20.57376327408119</v>
       </c>
     </row>

--- a/out_FPT/compare_sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26.xlsx
+++ b/out_FPT/compare_sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,70 +474,80 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Diesel_P_i_MF_mbar</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>Diesel_n_th_pct</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>E94H6_Speed_RPM</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>E94H6_Power_kW</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>E94H6_Consumo_kg_h</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>E94H6_Consumo_L_h</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>E94H6_Custo_R_h</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>E94H6_Custo_R_kWh</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>E94H6_Air_kg_h</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>E94H6_Air_kg_h_kW</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>E94H6_P_i_MF_mbar</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
         <is>
           <t>E94H6_n_th_pct</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_R_h</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_pct</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_R_kWh</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_R_kWh_pct</t>
         </is>
@@ -582,45 +592,51 @@
         <v>3.862228663873061</v>
       </c>
       <c r="L2" t="n">
+        <v>1383.7706061</v>
+      </c>
+      <c r="M2" t="n">
         <v>43.21582376606398</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>899.965</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>153.0359</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>59.591</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>73.66007416563659</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>154.6861557478368</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>1.010783455044449</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>493.8484</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>3.227010132916525</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
+        <v>626.0135</v>
+      </c>
+      <c r="W2" t="n">
         <v>37.58201332579686</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>-113.8359507901702</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>-42.39351175135284</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
         <v>-0.256900819510987</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AA2" t="n">
         <v>-20.2653629667434</v>
       </c>
     </row>
@@ -663,45 +679,51 @@
         <v>4.136611124591413</v>
       </c>
       <c r="L3" t="n">
+        <v>1808.42287132</v>
+      </c>
+      <c r="M3" t="n">
         <v>44.48653525713356</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>999.899</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>182.1889</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>70.161</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>86.72558714462299</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>182.1237330037083</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>0.9996423108307273</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>577.2861</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>3.168612906713856</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
+        <v>696.9444</v>
+      </c>
+      <c r="W3" t="n">
         <v>38.00086977651749</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>-135.379352970688</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>-42.63875185818039</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>-0.2318318843059595</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>-18.82555763015622</v>
       </c>
     </row>
@@ -744,45 +766,51 @@
         <v>4.439412673420192</v>
       </c>
       <c r="L4" t="n">
+        <v>2068.45330718</v>
+      </c>
+      <c r="M4" t="n">
         <v>44.80652170493985</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>1100.059</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>236.6207</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>90.709</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>112.1248454882571</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>235.4621755253399</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>0.9951038752118473</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>732.7568</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>3.096756961669034</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
+        <v>966.657</v>
+      </c>
+      <c r="W4" t="n">
         <v>38.17418283984513</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>-113.849790921741</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>-32.5925825215005</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>-0.2275757284619757</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>-18.61286699951254</v>
       </c>
     </row>
@@ -825,45 +853,51 @@
         <v>4.351854783728491</v>
       </c>
       <c r="L5" t="n">
+        <v>2103.78106115</v>
+      </c>
+      <c r="M5" t="n">
         <v>44.54043869545165</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>1199.668</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>261.7221</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>99.86499999999999</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>123.442521631644</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>259.2292954264524</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>0.9904753760819295</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>802.8339999999999</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>3.067505571749577</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
+        <v>1003.726</v>
+      </c>
+      <c r="W5" t="n">
         <v>38.35257109292667</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>-134.8767043913437</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>-34.22345877852664</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>-0.2395084724110762</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>-19.47248922858016</v>
       </c>
     </row>
@@ -906,45 +940,51 @@
         <v>4.337543110523877</v>
       </c>
       <c r="L6" t="n">
+        <v>2108.71964232</v>
+      </c>
+      <c r="M6" t="n">
         <v>44.29541275227747</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1300.024</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>280.1731</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>107.281</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>132.6093943139679</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>278.4797280593326</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>0.9939559795688186</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>859.04</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>3.066104490402541</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
+        <v>1003.352</v>
+      </c>
+      <c r="W6" t="n">
         <v>38.21826927733208</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>-149.5429293920391</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>-34.9380872224104</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>-0.2428316875103567</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>-19.63406443757911</v>
       </c>
     </row>
@@ -987,45 +1027,51 @@
         <v>4.332122930443129</v>
       </c>
       <c r="L7" t="n">
+        <v>2087.90902829</v>
+      </c>
+      <c r="M7" t="n">
         <v>43.92148191895775</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>1400.075</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>300.4143</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>115.281</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>142.4981458590853</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>299.2461063040791</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>0.9961113911823742</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>924.624</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>3.07782951743642</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
+        <v>1029.969</v>
+      </c>
+      <c r="W7" t="n">
         <v>38.1355715969526</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>-159.0279808018529</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>-34.70149966500132</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>-0.251205816859098</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>-20.13968982706007</v>
       </c>
     </row>
@@ -1068,45 +1114,51 @@
         <v>4.347692441495634</v>
       </c>
       <c r="L8" t="n">
+        <v>2090.40048932</v>
+      </c>
+      <c r="M8" t="n">
         <v>43.32666532362657</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>1500.016</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>301.1655</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>116.68</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>144.2274412855377</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>302.8776266996292</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>1.00568500276303</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>933.568</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>3.099850414473105</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
+        <v>945.126</v>
+      </c>
+      <c r="W8" t="n">
         <v>37.77254028111073</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>-188.6036641584247</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>-38.37453585041873</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>-0.2587561858443008</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>-20.46407442083548</v>
       </c>
     </row>
@@ -1149,45 +1201,51 @@
         <v>4.456480230588814</v>
       </c>
       <c r="L9" t="n">
+        <v>2003.24394734</v>
+      </c>
+      <c r="M9" t="n">
         <v>42.7827691460166</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>1600.038</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>300.3554</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>117.308</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>145.0037082818294</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>304.5077873918418</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>1.013824913392074</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>939.66</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>3.12849377770468</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
+        <v>871.4739999999999</v>
+      </c>
+      <c r="W9" t="n">
         <v>37.46926789348365</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>-200.4422911503153</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>-39.69546687249021</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
         <v>-0.2666910815689301</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
         <v>-20.8268450076683</v>
       </c>
     </row>
@@ -1230,45 +1288,51 @@
         <v>4.53941845037895</v>
       </c>
       <c r="L10" t="n">
+        <v>1872.93741169</v>
+      </c>
+      <c r="M10" t="n">
         <v>42.52423108019509</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>1699.999</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>296.0968</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>117.119</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>144.770086526576</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>304.0171817058097</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>1.026749298559828</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>935.774</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>3.16036512383788</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
+        <v>791.2596</v>
+      </c>
+      <c r="W10" t="n">
         <v>36.99761697452185</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>-201.5752495973791</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>-39.86911929789162</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
         <v>-0.2615519548333953</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>-20.30208028941215</v>
       </c>
     </row>
@@ -1311,45 +1375,51 @@
         <v>4.661451409354044</v>
       </c>
       <c r="L11" t="n">
+        <v>1824.85529229</v>
+      </c>
+      <c r="M11" t="n">
         <v>41.97438206424157</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>1799.979</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>291.8231</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>116.542</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>144.0568603213844</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>302.5194066749073</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>1.036653392671476</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>931.751</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>3.192862388207102</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
+        <v>722.6549</v>
+      </c>
+      <c r="W11" t="n">
         <v>36.64414503972399</v>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
         <v>-212.5273480354093</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>-41.26370006057864</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>-0.2685241348106859</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>-20.57376327408119</v>
       </c>
     </row>

--- a/out_FPT/compare_sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26.xlsx
+++ b/out_FPT/compare_sway_p8_full_load_curve_brazil_397kw_d85b15__vs__p251191_c13_etanol_full_load_curve_rev_26.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AE11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,75 +479,95 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Diesel_Eta_v_pct</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Diesel_Q_intercooler_kW</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>Diesel_n_th_pct</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>E94H6_Speed_RPM</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>E94H6_Power_kW</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>E94H6_Consumo_kg_h</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>E94H6_Consumo_L_h</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>E94H6_Custo_R_h</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>E94H6_Custo_R_kWh</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>E94H6_Air_kg_h</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>E94H6_Air_kg_h_kW</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>E94H6_P_i_MF_mbar</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>E94H6_Eta_v_pct</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>E94H6_Q_intercooler_kW</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
         <is>
           <t>E94H6_n_th_pct</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_R_h</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_pct</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_R_kWh</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Economia_vs_Diesel_R_kWh_pct</t>
         </is>
@@ -595,48 +615,60 @@
         <v>1383.7706061</v>
       </c>
       <c r="M2" t="n">
+        <v>199.4328866534262</v>
+      </c>
+      <c r="N2" t="n">
+        <v>25.99995209197379</v>
+      </c>
+      <c r="O2" t="n">
         <v>43.21582376606398</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>899.965</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>153.0359</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>59.591</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>73.66007416563659</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>154.6861557478368</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>1.010783455044449</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>493.8484</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>3.227010132916525</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>626.0135</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
+        <v>125.9094696987295</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>6.396908493687032</v>
+      </c>
+      <c r="AA2" t="n">
         <v>37.58201332579686</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AB2" t="n">
         <v>-113.8359507901702</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AC2" t="n">
         <v>-42.39351175135284</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AD2" t="n">
         <v>-0.256900819510987</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AE2" t="n">
         <v>-20.2653629667434</v>
       </c>
     </row>
@@ -682,48 +714,60 @@
         <v>1808.42287132</v>
       </c>
       <c r="M3" t="n">
+        <v>237.7665274826089</v>
+      </c>
+      <c r="N3" t="n">
+        <v>39.21109490130724</v>
+      </c>
+      <c r="O3" t="n">
         <v>44.48653525713356</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>999.899</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>182.1889</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>70.161</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>86.72558714462299</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>182.1237330037083</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.9996423108307273</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>577.2861</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>3.168612906713856</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>696.9444</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
+        <v>132.4059801264863</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>8.514083455979099</v>
+      </c>
+      <c r="AA3" t="n">
         <v>38.00086977651749</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AB3" t="n">
         <v>-135.379352970688</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AC3" t="n">
         <v>-42.63875185818039</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AD3" t="n">
         <v>-0.2318318843059595</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AE3" t="n">
         <v>-18.82555763015622</v>
       </c>
     </row>
@@ -769,48 +813,60 @@
         <v>2068.45330718</v>
       </c>
       <c r="M4" t="n">
+        <v>260.4278275653932</v>
+      </c>
+      <c r="N4" t="n">
+        <v>49.21946241193401</v>
+      </c>
+      <c r="O4" t="n">
         <v>44.80652170493985</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>1100.059</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>236.6207</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>90.709</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>112.1248454882571</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>235.4621755253399</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.9951038752118473</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>732.7568</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>3.096756961669034</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>966.657</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
+        <v>152.8105691663256</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>15.23641710058327</v>
+      </c>
+      <c r="AA4" t="n">
         <v>38.17418283984513</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AB4" t="n">
         <v>-113.849790921741</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AC4" t="n">
         <v>-32.5925825215005</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AD4" t="n">
         <v>-0.2275757284619757</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AE4" t="n">
         <v>-18.61286699951254</v>
       </c>
     </row>
@@ -856,48 +912,60 @@
         <v>2103.78106115</v>
       </c>
       <c r="M5" t="n">
+        <v>264.1959399479355</v>
+      </c>
+      <c r="N5" t="n">
+        <v>53.55340502049638</v>
+      </c>
+      <c r="O5" t="n">
         <v>44.54043869545165</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>1199.668</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>261.7221</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>99.86499999999999</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>123.442521631644</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>259.2292954264524</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0.9904753760819295</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>802.8339999999999</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>3.067505571749577</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>1003.726</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
+        <v>153.3635080573405</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>17.74821902428575</v>
+      </c>
+      <c r="AA5" t="n">
         <v>38.35257109292667</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AB5" t="n">
         <v>-134.8767043913437</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AC5" t="n">
         <v>-34.22345877852664</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AD5" t="n">
         <v>-0.2395084724110762</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AE5" t="n">
         <v>-19.47248922858016</v>
       </c>
     </row>
@@ -943,48 +1011,60 @@
         <v>2108.71964232</v>
       </c>
       <c r="M6" t="n">
+        <v>263.636130795378</v>
+      </c>
+      <c r="N6" t="n">
+        <v>57.08083544388736</v>
+      </c>
+      <c r="O6" t="n">
         <v>44.29541275227747</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>1300.024</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>280.1731</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>107.281</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>132.6093943139679</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>278.4797280593326</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>0.9939559795688186</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>859.04</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>3.066104490402541</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>1003.352</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
+        <v>151.3299523887224</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>19.44642153696666</v>
+      </c>
+      <c r="AA6" t="n">
         <v>38.21826927733208</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AB6" t="n">
         <v>-149.5429293920391</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AC6" t="n">
         <v>-34.9380872224104</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AD6" t="n">
         <v>-0.2428316875103567</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AE6" t="n">
         <v>-19.63406443757911</v>
       </c>
     </row>
@@ -1030,48 +1110,60 @@
         <v>2087.90902829</v>
       </c>
       <c r="M7" t="n">
+        <v>261.1287621659193</v>
+      </c>
+      <c r="N7" t="n">
+        <v>59.57143091889137</v>
+      </c>
+      <c r="O7" t="n">
         <v>43.92148191895775</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>1400.075</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>300.4143</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>115.281</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>142.4981458590853</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>299.2461063040791</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>0.9961113911823742</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>924.624</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>3.07782951743642</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>1029.969</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
+        <v>151.4528223795006</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>21.8214326817</v>
+      </c>
+      <c r="AA7" t="n">
         <v>38.1355715969526</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AB7" t="n">
         <v>-159.0279808018529</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AC7" t="n">
         <v>-34.70149966500132</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AD7" t="n">
         <v>-0.251205816859098</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AE7" t="n">
         <v>-20.13968982706007</v>
       </c>
     </row>
@@ -1117,48 +1209,60 @@
         <v>2090.40048932</v>
       </c>
       <c r="M8" t="n">
+        <v>260.6430087969362</v>
+      </c>
+      <c r="N8" t="n">
+        <v>63.15925558260871</v>
+      </c>
+      <c r="O8" t="n">
         <v>43.32666532362657</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>1500.016</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>301.1655</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>116.68</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>144.2274412855377</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>302.8776266996292</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>1.00568500276303</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>933.568</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>3.099850414473105</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>945.126</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
+        <v>142.6978264604757</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20.80657339648533</v>
+      </c>
+      <c r="AA8" t="n">
         <v>37.77254028111073</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AB8" t="n">
         <v>-188.6036641584247</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AC8" t="n">
         <v>-38.37453585041873</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AD8" t="n">
         <v>-0.2587561858443008</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AE8" t="n">
         <v>-20.46407442083548</v>
       </c>
     </row>
@@ -1204,48 +1308,60 @@
         <v>2003.24394734</v>
       </c>
       <c r="M9" t="n">
+        <v>254.307230603555</v>
+      </c>
+      <c r="N9" t="n">
+        <v>65.04774618537127</v>
+      </c>
+      <c r="O9" t="n">
         <v>42.7827691460166</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>1600.038</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>300.3554</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>117.308</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>145.0037082818294</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>304.5077873918418</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>1.013824913392074</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>939.66</v>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
         <v>3.12849377770468</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>871.4739999999999</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
+        <v>134.7685023601441</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>19.76882940174999</v>
+      </c>
+      <c r="AA9" t="n">
         <v>37.46926789348365</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AB9" t="n">
         <v>-200.4422911503153</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AC9" t="n">
         <v>-39.69546687249021</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AD9" t="n">
         <v>-0.2666910815689301</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AE9" t="n">
         <v>-20.8268450076683</v>
       </c>
     </row>
@@ -1291,48 +1407,60 @@
         <v>1872.93741169</v>
       </c>
       <c r="M10" t="n">
+        <v>241.8846982364728</v>
+      </c>
+      <c r="N10" t="n">
+        <v>64.1654884816061</v>
+      </c>
+      <c r="O10" t="n">
         <v>42.52423108019509</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>1699.999</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>296.0968</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>117.119</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>144.770086526576</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>304.0171817058097</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>1.026749298559828</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>935.774</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>3.16036512383788</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>791.2596</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
+        <v>126.3173259000818</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>18.32208567917583</v>
+      </c>
+      <c r="AA10" t="n">
         <v>36.99761697452185</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AB10" t="n">
         <v>-201.5752495973791</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AC10" t="n">
         <v>-39.86911929789162</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AD10" t="n">
         <v>-0.2615519548333953</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AE10" t="n">
         <v>-20.30208028941215</v>
       </c>
     </row>
@@ -1378,48 +1506,60 @@
         <v>1824.85529229</v>
       </c>
       <c r="M11" t="n">
+        <v>236.7196328849409</v>
+      </c>
+      <c r="N11" t="n">
+        <v>66.41701487097963</v>
+      </c>
+      <c r="O11" t="n">
         <v>41.97438206424157</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>1799.979</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>291.8231</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>116.542</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>144.0568603213844</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>302.5194066749073</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>1.036653392671476</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>931.751</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>3.192862388207102</v>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
         <v>722.6549</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
+        <v>118.9052406400124</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>16.99069460301212</v>
+      </c>
+      <c r="AA11" t="n">
         <v>36.64414503972399</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AB11" t="n">
         <v>-212.5273480354093</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AC11" t="n">
         <v>-41.26370006057864</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AD11" t="n">
         <v>-0.2685241348106859</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AE11" t="n">
         <v>-20.57376327408119</v>
       </c>
     </row>
